--- a/BWI/bestwine_output/bestwine_Belarus.xlsx
+++ b/BWI/bestwine_output/bestwine_Belarus.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA24"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2926,6 +2926,95 @@
       </c>
       <c r="AA24" s="2" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Servisbytsnab, Ooo</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Servisbytsnab, Ooo</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>82265</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Minsk</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Minskaja voblasć, Minski rajon</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4 Vulitsa Kazintsa</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://sbswine.by</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>marketing@sbsfood.by</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>100950166</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sbswine/</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Pavel Iosifovich</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
